--- a/reports/excel/alarms/alarms_report_22-05-2026.xlsx
+++ b/reports/excel/alarms/alarms_report_22-05-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ALARMS_REPORT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALARMS_REPORT'!$A$1:$G$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALARMS_REPORT'!$A$1:$G$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1189,7 +1189,7 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AFI BRAKE MANUFACTURING SDN BHD</t>
+          <t>REDANG LAGOON RESORT</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>INV 7 - THIRD FLOOR</t>
+          <t>DONGLE-2102312EHS10N9115979</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>HV22B0337096</t>
+          <t>2102312EHS10N9115979</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>GRID LOSS</t>
+          <t>NETWORK CONNECTION ERROR</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-2102312EHS10N9115979</t>
+          <t>INV-ES22A0089681</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2102312EHS10N9115979</t>
+          <t>ES22A0089681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>NETWORK CONNECTION ERROR</t>
+          <t>GRID LOSS</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1263,32 +1263,32 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>REDANG LAGOON RESORT</t>
+          <t>LIAN FOO POULTRY FARM SDN BHD</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>KUALA TERENGGANU</t>
+          <t>MASJID TANAH</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>INV-ES22A0089681</t>
+          <t>DONGLE-BT2541519026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ES22A0089681</t>
+          <t>BT2541519026</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>GRID LOSS</t>
+          <t>NETWORK CONNECTION ERROR</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1310,22 +1310,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-BT2541519026</t>
+          <t>INV-ES2550000030</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>BT2541519026</t>
+          <t>ES2550000030</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>NETWORK CONNECTION ERROR</t>
+          <t>GRID LOSS</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>INV-ES2550000030</t>
+          <t>INV-ES25C0125116</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ES2550000030</t>
+          <t>ES25C0125116</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>INV-ES25C0125116</t>
+          <t>INV-ES25C0125117</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ES25C0125116</t>
+          <t>ES25C0125117</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1411,59 +1411,59 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIAN FOO POULTRY FARM SDN BHD</t>
+          <t>FIBERTEX PHASE 2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MASJID TANAH</t>
+          <t>NILAI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>INV-ES25C0125117</t>
+          <t>INVERTER 2 L3 OLD</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ES25C0125117</t>
+          <t>6T2379019735</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>GRID LOSS</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
+          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>MINOR</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIBERTEX PHASE 2</t>
+          <t>PKT 12 WAVES</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>NILAI</t>
+          <t>PENANG</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 2 L3 OLD</t>
+          <t>INVERTER 1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6T2379019735</t>
+          <t>6T2459004867</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 1</t>
+          <t>INVERTER 10</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6T2459004867</t>
+          <t>6T2449041556</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 10</t>
+          <t>INVERTER 2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6T2449041556</t>
+          <t>6T2459004831</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 2</t>
+          <t>INVERTER 3</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6T2459004831</t>
+          <t>6T2449041406</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 3</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6T2449041406</t>
+          <t>ES2470045168</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>INVERTER 5</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ES2470045168</t>
+          <t>6T2459004824</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 5</t>
+          <t>INVERTER 6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6T2459004824</t>
+          <t>ES2470045204</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 6</t>
+          <t>INVERTER 7</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ES2470045204</t>
+          <t>6T2449033633</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 7</t>
+          <t>INVERTER 8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6T2449033633</t>
+          <t>6T2459004809</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 8</t>
+          <t>INVERTER 9</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>6T2459004809</t>
+          <t>6T2449032075</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1818,59 +1818,59 @@
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PKT 12 WAVES</t>
+          <t>PENGERANG INDEPENDENT TERMINAL</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PENANG</t>
+          <t>PENGERANG</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 9</t>
+          <t>DONGLE-LAB</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6T2449032075</t>
+          <t>TA23B0087782</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>MINOR</t>
+          <t>NETWORK CONNECTION ERROR</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PENGERANG INDEPENDENT TERMINAL</t>
+          <t>MENARA PKNS PJ</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PENGERANG</t>
+          <t>PETALING JAYA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-LAB</t>
+          <t>LOGGER-102466288020</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>TA23B0087782</t>
+          <t>102466288020</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1892,37 +1892,37 @@
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MENARA PKNS PJ</t>
+          <t>IOI MALL PUCHONG (NEW WING) PHASE 2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PETALING JAYA</t>
+          <t>PUCHONG</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>LOGGER-102466288020</t>
+          <t>INVERTER 3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>102466288020</t>
+          <t>GR2569071111</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>NETWORK CONNECTION ERROR</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
+          <t>STRING LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>WARNING</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 3</t>
+          <t>INVERTER 4</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>GR2569071111</t>
+          <t>GR2569071069</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IOI MALL PUCHONG (NEW WING) PHASE 2</t>
+          <t>IOI MALL PUCHONG (OLD WING)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2198,27 +2198,27 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 4</t>
+          <t>INVERTER 1 - TERA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GR2569071069</t>
+          <t>BN2461065466</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>STRING LOSS</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>WARNING</t>
+          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>MINOR</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 1 - TERA</t>
+          <t>INVERTER 10 - TERA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>BN2461065466</t>
+          <t>6T2469039407</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 10 - TERA</t>
+          <t>INVERTER 11 - TERA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>6T2469039407</t>
+          <t>BN2461066739</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 11 - TERA</t>
+          <t>INVERTER 12 - TERA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>BN2461066739</t>
+          <t>BN2461066801</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 12 - TERA</t>
+          <t>INVERTER 2 - TERA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BN2461066801</t>
+          <t>BN2461066770</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 2 - TERA</t>
+          <t>INVERTER 21 R1-TERA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BN2461066770</t>
+          <t>6T2599057796</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 21 R1-TERA</t>
+          <t>INVERTER 3 R1 - TERA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>6T2599057796</t>
+          <t>BN2521059950</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 3 R1 - TERA</t>
+          <t>INVERTER 4 - TERA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BN2521059950</t>
+          <t>6T2479017517</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 4 - TERA</t>
+          <t>INVERTER 5 - TERA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>6T2479017517</t>
+          <t>BN2461066760</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 5 - TERA</t>
+          <t>INVERTER 6 - TERA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>BN2461066760</t>
+          <t>BN2461066754</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 6 - TERA</t>
+          <t>INVERTER 7 - TERA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BN2461066754</t>
+          <t>6T2479017524</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 7 - TERA</t>
+          <t>INVERTER 8 - TERA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>6T2479017524</t>
+          <t>BN2461065428</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 8 - TERA</t>
+          <t>INVERTER 9 - TERA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>BN2461065428</t>
+          <t>6T2479017523</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2669,37 +2669,37 @@
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IOI MALL PUCHONG (OLD WING)</t>
+          <t>MARINE GOLD SDN BHD</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PUCHONG</t>
+          <t>RAWANG</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 9 - TERA</t>
+          <t>DONGLE-HV2310773587</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>6T2479017523</t>
+          <t>HV2310773587</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>MINOR</t>
+          <t>NETWORK CONNECTION ERROR</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-HV2310773587</t>
+          <t>DONGLE-HV2310776105</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>HV2310773587</t>
+          <t>HV2310776105</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-HV2310776105</t>
+          <t>DONGLE-HV2310776109</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>HV2310776105</t>
+          <t>HV2310776109</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-HV2310776109</t>
+          <t>DONGLE-TA2340291437</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>HV2310776109</t>
+          <t>TA2340291437</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-TA2340291437</t>
+          <t>DONGLE-TA2340293153</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>TA2340291437</t>
+          <t>TA2340293153</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-TA2340293153</t>
+          <t>DONGLE-TA2340293476</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>TA2340293153</t>
+          <t>TA2340293476</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2891,37 +2891,37 @@
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MARINE GOLD SDN BHD</t>
+          <t>THP MEDICAL</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>RAWANG</t>
+          <t>SIMPANG AMPAT</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-TA2340293476</t>
+          <t>VASOLAR INV 1</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>TA2340293476</t>
+          <t>6T2279009011</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>NETWORK CONNECTION ERROR</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
+          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>MINOR</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VASOLAR INV 1</t>
+          <t>VASOLAR INV 2</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>6T2279009011</t>
+          <t>6T2279008977</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VASOLAR INV 2</t>
+          <t>VASOLAR INV 3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>6T2279008977</t>
+          <t>6T2279009018</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3002,59 +3002,59 @@
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>THP MEDICAL</t>
+          <t>BOILERMECH LOT 873</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SIMPANG AMPAT</t>
+          <t>SUBANG JAYA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VASOLAR INV 3</t>
+          <t>LOGGER-102516002824</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>6T2279009018</t>
+          <t>102516002824</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>UPGRADE FAILED OR VERSION MISMATCH</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>MINOR</t>
+          <t>NETWORK CONNECTION ERROR</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
         </is>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>BOILERMECH LOT 873</t>
+          <t>KILANG BATU BATA</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SUBANG JAYA</t>
+          <t>SUNGAI SIPUT</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>LOGGER-102516002824</t>
+          <t>DONGLE-TA2510047367</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>102516002824</t>
+          <t>TA2510047367</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3076,32 +3076,32 @@
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KILANG BATU BATA</t>
+          <t>QL FARM SDN BHD</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SUNGAI SIPUT</t>
+          <t>TAWAU</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>DONGLE-TA2510047367</t>
+          <t>INVERTER 1</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>TA2510047367</t>
+          <t>ES2580051653</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>NETWORK CONNECTION ERROR</t>
+          <t>GRID LOSS</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 1</t>
+          <t>INVERTER 2</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ES2580051653</t>
+          <t>ES2580051643</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>INVERTER 2</t>
+          <t>INVERTER3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>ES2580051643</t>
+          <t>ES2490076207</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3197,22 +3197,22 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>INVERTER3</t>
+          <t>LOGGER-102466853213</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>ES2490076207</t>
+          <t>102466853213</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>GRID LOSS</t>
+          <t>NETWORK CONNECTION ERROR</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -3221,45 +3221,8 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>QL FARM SDN BHD</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>TAWAU</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>LOGGER-102466853213</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>102466853213</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>999999999</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>NETWORK CONNECTION ERROR</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G75"/>
+  <autoFilter ref="A1:G74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>